--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_193_R20.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_193_R20.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6172</v>
+        <v>5.44</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1231</v>
+        <v>5.7443</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.506</v>
+        <v>-0.3043</v>
       </c>
       <c r="G2" t="n">
         <v>4.3489</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5772</v>
+        <v>0.2456</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6721</v>
+        <v>-0.051</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0949</v>
+        <v>0.2965</v>
       </c>
       <c r="V2" t="n">
         <v>2.933</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9276</v>
+        <v>3.8588</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9928</v>
+        <v>2.2601</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9348</v>
+        <v>1.5987</v>
       </c>
       <c r="G3" t="n">
         <v>5.5933</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1142</v>
+        <v>-0.183</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5975</v>
+        <v>-0.3301</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4832</v>
+        <v>0.1472</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.766</v>
+        <v>2.0033</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9917</v>
+        <v>1.8003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7743</v>
+        <v>0.203</v>
       </c>
       <c r="G4" t="n">
         <v>2.0963</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0588</v>
+        <v>1.2962</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6122</v>
+        <v>0.4208</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4466</v>
+        <v>0.8753</v>
       </c>
       <c r="V4" t="n">
         <v>0.9304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2487</v>
+        <v>1.5926</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.092</v>
+        <v>2.0693</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3408</v>
+        <v>-0.4766</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1819</v>
+        <v>2.2592</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4309</v>
+        <v>1.1418</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6128</v>
+        <v>1.1175</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4386</v>
+        <v>2.5488</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7023</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.141</v>
+        <v>1.9606</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7432</v>
+        <v>-0.2895</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2714</v>
+        <v>0.5536</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4718</v>
+        <v>-0.8431</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4872</v>
+        <v>-0.3804</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>-0.4795</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1885</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.232</v>
+        <v>1.5422</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8766</v>
+        <v>0.1006</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6447000000000001</v>
+        <v>1.4416</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2592</v>
+        <v>1.1819</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1418</v>
+        <v>-0.4309</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1175</v>
+        <v>1.6128</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5488</v>
+        <v>0.4386</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5881999999999999</v>
+        <v>-0.7023</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9606</v>
+        <v>1.141</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2895</v>
+        <v>0.7432</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5536</v>
+        <v>0.2714</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8431</v>
+        <v>0.4718</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7411</v>
+        <v>-0.1937</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6721</v>
+        <v>-0.1061</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0876</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9066</v>
+        <v>1.4195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5846</v>
+        <v>1.1311</v>
       </c>
       <c r="F7" t="n">
-        <v>0.322</v>
+        <v>0.2884</v>
       </c>
       <c r="G7" t="n">
         <v>2.0741</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0619</v>
+        <v>0.4509</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8215</v>
+        <v>-0.275</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="V7" t="n">
         <v>1.214</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2369</v>
+        <v>0.5523</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5573</v>
+        <v>1.1785</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7942</v>
+        <v>-0.6261</v>
       </c>
       <c r="G8" t="n">
         <v>0.1254</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6664</v>
+        <v>0.1228</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9709</v>
+        <v>-0.3497</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3044</v>
+        <v>0.4725</v>
       </c>
       <c r="V8" t="n">
         <v>0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.434</v>
+        <v>-1.0562</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1257</v>
+        <v>-0.8151</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3083</v>
+        <v>-0.2411</v>
       </c>
       <c r="G9" t="n">
         <v>1.4673</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1318</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2987</v>
+        <v>0.0119</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0666</v>
+        <v>-1.597</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1807</v>
+        <v>-2.6775</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1141</v>
+        <v>1.0805</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4043</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.286</v>
+        <v>0.1836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0455</v>
+        <v>-0.5423</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.726</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1855</v>
+        <v>-3.8602</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2479</v>
+        <v>-2.1915</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9376</v>
+        <v>-1.6687</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4118</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6001</v>
+        <v>-0.0747</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9752</v>
+        <v>0.0316</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3752</v>
+        <v>-0.1063</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7501</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.775099999999998</v>
+        <v>9.895299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>7.479799999999999</v>
+        <v>8.600100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2952</v>
+        <v>1.2954</v>
       </c>
       <c r="G12" t="n">
         <v>15.3303</v>
@@ -1366,7 +1366,7 @@
         <v>22.9618</v>
       </c>
       <c r="K12" t="n">
-        <v>7.1533</v>
+        <v>7.153300000000002</v>
       </c>
       <c r="L12" t="n">
         <v>15.8086</v>
@@ -1375,7 +1375,7 @@
         <v>-7.6314</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5483999999999994</v>
+        <v>0.5483999999999997</v>
       </c>
       <c r="O12" t="n">
         <v>-8.18</v>
@@ -1390,13 +1390,13 @@
         <v>11.5977</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2153</v>
+        <v>1.3355</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.789600000000001</v>
+        <v>-1.6694</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0047</v>
+        <v>3.0051</v>
       </c>
       <c r="V12" t="n">
         <v>2.5076</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. BLATT</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0919</v>
+        <v>1.5798</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7815</v>
+        <v>2.6648</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6897</v>
+        <v>-1.085</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5608</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1465</v>
+        <v>-0.4404</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7073</v>
+        <v>1.2947</v>
       </c>
       <c r="J13" t="n">
-        <v>7.3706</v>
+        <v>4.5712</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3983</v>
+        <v>0.9579</v>
       </c>
       <c r="L13" t="n">
-        <v>5.9723</v>
+        <v>3.6133</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.8099</v>
+        <v>-3.7169</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5448</v>
+        <v>-1.3983</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.2651</v>
+        <v>-2.3186</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3195</v>
+        <v>2.5515</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8606</v>
+        <v>-0.6662</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2696</v>
+        <v>-0.7466</v>
       </c>
       <c r="U13" t="n">
-        <v>0.409</v>
+        <v>0.0804</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9824000000000001</v>
+        <v>1.3362</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2156</v>
+        <v>0.5694</v>
       </c>
       <c r="F14" t="n">
         <v>0.7668</v>
@@ -1546,10 +1546,10 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3145</v>
+        <v>0.6684</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2082</v>
+        <v>0.1456</v>
       </c>
       <c r="U14" t="n">
         <v>0.5228</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>T. BLATT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9214</v>
+        <v>1.3284</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7422</v>
+        <v>4.2533</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8208</v>
+        <v>-2.9249</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8388</v>
+        <v>3.5608</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9014</v>
+        <v>-0.1465</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.7403</v>
+        <v>3.7073</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5839</v>
+        <v>7.3706</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1126</v>
+        <v>1.3983</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5286999999999999</v>
+        <v>5.9723</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4227</v>
+        <v>-3.8099</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2112</v>
+        <v>-1.5448</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2116</v>
+        <v>-2.2651</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7112000000000001</v>
+        <v>-0.624</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1968</v>
+        <v>-0.7978</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5144</v>
+        <v>0.1737</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4254</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.654</v>
+        <v>0.4667</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0751</v>
+        <v>1.3883</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4211</v>
+        <v>-0.9216</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8542999999999999</v>
+        <v>-1.8388</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4404</v>
+        <v>0.9014</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2947</v>
+        <v>-2.7403</v>
       </c>
       <c r="J16" t="n">
-        <v>4.5712</v>
+        <v>0.5839</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9579</v>
+        <v>1.1126</v>
       </c>
       <c r="L16" t="n">
-        <v>3.6133</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.7169</v>
+        <v>-2.4227</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3983</v>
+        <v>-0.2112</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3186</v>
+        <v>-2.2116</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.592</v>
+        <v>0.2566</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3364</v>
+        <v>-0.1571</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2557</v>
+        <v>0.4136</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.4254</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.9615</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3283</v>
+        <v>-0.1584</v>
       </c>
       <c r="E17" t="n">
-        <v>0.698</v>
+        <v>-1.9489</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3697</v>
+        <v>1.7905</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1614</v>
+        <v>-1.1227</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4848</v>
+        <v>-0.4201</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6462</v>
+        <v>-0.7026</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1145</v>
+        <v>-0.3294</v>
       </c>
       <c r="K17" t="n">
-        <v>0.864</v>
+        <v>-0.3662</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2759</v>
+        <v>-0.7933</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3792</v>
+        <v>-0.0539</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8966</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P17" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R17" t="n">
         <v>2.0876</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.3195</v>
-      </c>
       <c r="S17" t="n">
-        <v>1.0104</v>
+        <v>0.2684</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2794</v>
+        <v>-0.2278</v>
       </c>
       <c r="U17" t="n">
-        <v>0.731</v>
+        <v>0.4962</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.165</v>
+        <v>-0.2437</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9272</v>
+        <v>0.4621</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7623</v>
+        <v>-0.7058</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.2105</v>
+        <v>-1.1614</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4205</v>
+        <v>0.4848</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.79</v>
+        <v>-1.6462</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4848</v>
+        <v>0.1145</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.201</v>
+        <v>0.864</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6859</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.6953</v>
+        <v>-1.2759</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2195</v>
+        <v>-0.3792</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4759</v>
+        <v>-0.8966</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5515</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6822</v>
+        <v>0.4384</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2284</v>
+        <v>0.0435</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4538</v>
+        <v>0.3949</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8147</v>
+        <v>-0.7108</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.3028</v>
+        <v>1.2195</v>
       </c>
       <c r="F19" t="n">
-        <v>1.488</v>
+        <v>-1.9303</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1227</v>
+        <v>-3.2105</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4201</v>
+        <v>-1.4205</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7026</v>
+        <v>-1.79</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3294</v>
+        <v>0.4848</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3662</v>
+        <v>-0.201</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.6859</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7933</v>
+        <v>-3.6953</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0539</v>
+        <v>-1.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-2.4759</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3879</v>
+        <v>-0.1935</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5816</v>
+        <v>-0.4793</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1937</v>
+        <v>0.2858</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4671</v>
+        <v>-2.9953</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7017</v>
+        <v>-0.2299</v>
       </c>
       <c r="F20" t="n">
         <v>-2.7654</v>
@@ -2014,10 +2014,10 @@
         <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3091</v>
+        <v>-0.8373</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3443</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U20" t="n">
         <v>0.0351</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6523</v>
+        <v>-4.2085</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8117</v>
+        <v>-3.4015</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8406</v>
+        <v>-0.8070000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>-4.5623</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8404</v>
+        <v>0.2842</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6844</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.156</v>
+        <v>0.1896</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9839</v>
+        <v>-5.1697</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9188</v>
+        <v>-6.2726</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9349</v>
+        <v>1.1029</v>
       </c>
       <c r="G22" t="n">
         <v>-3.2719</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3756</v>
+        <v>0.1898</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3462</v>
+        <v>-0.0077</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0294</v>
+        <v>0.1975</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.774999999999999</v>
+        <v>-8.7753</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.295400000000002</v>
+        <v>-1.2955</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.479900000000002</v>
+        <v>-7.479800000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-15.3303</v>
@@ -2248,13 +2248,13 @@
         <v>20.8758</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2153</v>
+        <v>-0.2152</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0049</v>
+        <v>-3.005</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7895</v>
+        <v>2.7896</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5076</v>
